--- a/examples/retail.xlsx
+++ b/examples/retail.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -423,7 +423,10 @@
         <v>taxed_revenue</v>
       </c>
       <c r="H1" t="str">
-        <v>avg_qty</v>
+        <v>running_revenue</v>
+      </c>
+      <c r="I1" t="str">
+        <v>previous_revenue</v>
       </c>
     </row>
     <row r="2">
@@ -443,13 +446,13 @@
         <v>5</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>14.249999999999998</v>
       </c>
       <c r="G2">
         <v>16.2</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>14.249999999999998</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +472,16 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <v>21.6</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>33.25</v>
+      </c>
+      <c r="I3">
+        <v>14.249999999999998</v>
       </c>
     </row>
     <row r="4">
@@ -495,13 +501,16 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>22.799999999999997</v>
       </c>
       <c r="G4">
         <v>25.92</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>45.599999999999994</v>
+      </c>
+      <c r="I4">
+        <v>22.799999999999997</v>
       </c>
     </row>
     <row r="5">
@@ -521,13 +530,13 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>22.799999999999997</v>
       </c>
       <c r="G5">
         <v>25.92</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>22.799999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -547,13 +556,16 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>13.299999999999999</v>
       </c>
       <c r="G6">
         <v>15.12</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>24.699999999999996</v>
+      </c>
+      <c r="I6">
+        <v>11.399999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -573,18 +585,18 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>11.399999999999999</v>
       </c>
       <c r="G7">
         <v>12.96</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>11.399999999999999</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -627,22 +639,22 @@
         <v>sales</v>
       </c>
       <c r="C2" t="str">
-        <v>Price and quantity bar demo</v>
+        <v>Revenue and running revenue bar demo</v>
       </c>
       <c r="D2" t="str">
-        <v>price</v>
+        <v>revenue</v>
       </c>
       <c r="E2" t="str">
-        <v>qty</v>
+        <v>running_revenue</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>price,qty</v>
+        <v>revenue,running_revenue</v>
       </c>
       <c r="H2" t="str">
-        <v>{"$schema":"https://vega.github.io/schema/vega-lite/v5.json","mark":"bar","title":"Price and quantity bar demo","data":{"values":[{"price":3,"qty":5},{"price":2,"qty":10},{"price":3,"qty":8},{"price":4,"qty":6},{"price":2,"qty":7},{"price":4,"qty":3}]},"encoding":{"x":{"field":"price","type":"quantitative"},"y":{"field":"qty","type":"quantitative"}}}</v>
+        <v>{"$schema":"https://vega.github.io/schema/vega-lite/v5.json","mark":"bar","title":"Revenue and running revenue bar demo","data":{"values":[{"revenue":14.249999999999998,"running_revenue":14.249999999999998},{"revenue":19,"running_revenue":33.25},{"revenue":22.799999999999997,"running_revenue":45.599999999999994},{"revenue":22.799999999999997,"running_revenue":22.799999999999997},{"revenue":13.299999999999999,"running_revenue":24.699999999999996},{"revenue":11.399999999999999,"running_revenue":11.399999999999999}]},"encoding":{"x":{"field":"revenue","type":"quantitative"},"y":{"field":"running_revenue","type":"quantitative"}}}</v>
       </c>
     </row>
   </sheetData>
